--- a/data/trans_bre/IP19C06-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP19C06-Clase-trans_bre.xlsx
@@ -675,7 +675,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,85; 10,46</t>
+          <t>1,69; 10,68</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,83; 1,87</t>
+          <t>-4,62; 1,84</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-4,64; 2,65</t>
+          <t>-4,56; 2,65</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,39</t>
+          <t>0,0; 9,75</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -965,7 +965,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,85</t>
+          <t>0,0; 4,33</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -975,7 +975,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,88</t>
+          <t>0,0; 3,17</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1060,22 +1060,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,81; 0,0</t>
+          <t>-4,51; 0,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-7,5; 0,0</t>
+          <t>-7,2; 0,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,75</t>
+          <t>0,0; 5,66</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,25</t>
+          <t>0,0; 5,08</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-7,83; 0,0</t>
+          <t>-9,7; 0,0</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,54</t>
+          <t>0,0; 12,81</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,84</t>
+          <t>0,0; 9,76</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-12,45; 0,0</t>
+          <t>-14,83; 0,0</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1260,22 +1260,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 0,0</t>
+          <t>-1,54; 0,0</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 1,49</t>
+          <t>-0,75; 1,5</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,39</t>
+          <t>0,0; 1,45</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,16; 2,27</t>
+          <t>-0,13; 2,24</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1285,7 +1285,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-81,43; —</t>
+          <t>-81,09; —</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-57,0; —</t>
+          <t>-57,18; —</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP19C06-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP19C06-Clase-trans_bre.xlsx
@@ -675,7 +675,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,69; 10,68</t>
+          <t>1,62; 10,43</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-4,62; 1,84</t>
+          <t>-3,73; 1,83</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-4,56; 2,65</t>
+          <t>-4,46; 2,66</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,75</t>
+          <t>0,0; 10,79</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -965,7 +965,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,33</t>
+          <t>0,0; 3,83</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -975,7 +975,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,17</t>
+          <t>0,0; 3,2</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1060,22 +1060,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,51; 0,0</t>
+          <t>-4,21; 0,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-7,2; 0,0</t>
+          <t>-7,42; 0,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,66</t>
+          <t>0,0; 5,64</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,08</t>
+          <t>0,0; 4,17</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-9,7; 0,0</t>
+          <t>-9,71; 0,0</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,81</t>
+          <t>0,0; 13,2</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,76</t>
+          <t>0,0; 10,33</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-14,83; 0,0</t>
+          <t>-14,53; 0,0</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1260,22 +1260,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,54; 0,0</t>
+          <t>-1,25; 0,0</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 1,5</t>
+          <t>-0,83; 1,45</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,45</t>
+          <t>0,0; 1,31</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,13; 2,24</t>
+          <t>-0,15; 2,38</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1285,7 +1285,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-81,09; —</t>
+          <t>-79,74; —</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-57,18; —</t>
+          <t>-49,39; —</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP19C06-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP19C06-Clase-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4,6</t>
+          <t>4,68</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -675,7 +675,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,62; 10,43</t>
+          <t>1,97; 10,97</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-0,17</t>
+          <t>-0,11</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-11,75%</t>
+          <t>-8,14%</t>
         </is>
       </c>
     </row>
@@ -765,7 +765,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,73; 1,83</t>
+          <t>-3,83; 1,87</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-4,46; 2,66</t>
+          <t>-4,3; 2,62</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,79</t>
+          <t>0,0; 10,39</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1,0</t>
+          <t>0,95</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -965,7 +965,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,83</t>
+          <t>0,0; 3,85</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -975,7 +975,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,2</t>
+          <t>0,0; 3,74</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0,79</t>
+          <t>0,69</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1060,22 +1060,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,21; 0,0</t>
+          <t>-3,81; 0,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-7,42; 0,0</t>
+          <t>-7,5; 0,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,64</t>
+          <t>0,0; 6,75</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,17</t>
+          <t>0,0; 3,74</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-3,02</t>
+          <t>-1,46</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-9,71; 0,0</t>
+          <t>-7,83; 0,0</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,2</t>
+          <t>0,0; 15,54</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,33</t>
+          <t>0,0; 9,84</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-14,53; 0,0</t>
+          <t>-6,61; 0,0</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>0,99</t>
+          <t>1,1</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>199,75%</t>
+          <t>312,84%</t>
         </is>
       </c>
     </row>
@@ -1260,22 +1260,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 0,0</t>
+          <t>-1,27; 0,0</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 1,45</t>
+          <t>-0,72; 1,49</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,31</t>
+          <t>0,0; 1,39</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,15; 2,38</t>
+          <t>0,13; 2,42</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1285,7 +1285,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-79,74; —</t>
+          <t>-81,43; —</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-49,39; —</t>
+          <t>-40,63; —</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP19C06-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP19C06-Clase-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J18"/>
+  <dimension ref="A1:J25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,44 +619,24 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>4,68</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
+      <c r="C4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>4.682655692006615</v>
+      </c>
+      <c r="G4" s="6" t="inlineStr"/>
+      <c r="H4" s="6" t="inlineStr"/>
+      <c r="I4" s="6" t="inlineStr"/>
+      <c r="J4" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
         </is>
       </c>
     </row>
@@ -655,254 +644,114 @@
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>1,97; 10,97</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr"/>
+      <c r="D5" s="5" t="inlineStr"/>
+      <c r="E5" s="5" t="inlineStr"/>
+      <c r="F5" s="5" t="n">
+        <v>1.967839885397504</v>
+      </c>
+      <c r="G5" s="6" t="inlineStr"/>
+      <c r="H5" s="6" t="inlineStr"/>
+      <c r="I5" s="6" t="inlineStr"/>
+      <c r="J5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr"/>
+      <c r="D6" s="5" t="inlineStr"/>
+      <c r="E6" s="5" t="inlineStr"/>
+      <c r="F6" s="5" t="n">
+        <v>10.96598768104949</v>
+      </c>
+      <c r="G6" s="6" t="inlineStr"/>
+      <c r="H6" s="6" t="inlineStr"/>
+      <c r="I6" s="6" t="inlineStr"/>
+      <c r="J6" s="6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Grupo III</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>-0,27</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-0,11</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-22,89%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>-8,14%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-3,83; 1,87</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-4,3; 2,62</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>-0.2688610269182677</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>-0.1115047304808126</v>
+      </c>
+      <c r="G7" s="6" t="inlineStr"/>
+      <c r="H7" s="6" t="n">
+        <v>-0.2288607816362505</v>
+      </c>
+      <c r="I7" s="6" t="inlineStr"/>
+      <c r="J7" s="6" t="n">
+        <v>-0.08141708790464718</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Grupo IV y V</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>3,07</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr"/>
+      <c r="D8" s="5" t="n">
+        <v>-3.825784153994004</v>
+      </c>
+      <c r="E8" s="5" t="inlineStr"/>
+      <c r="F8" s="5" t="n">
+        <v>-4.300926529333748</v>
+      </c>
+      <c r="G8" s="6" t="inlineStr"/>
+      <c r="H8" s="6" t="inlineStr"/>
+      <c r="I8" s="6" t="inlineStr"/>
+      <c r="J8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 10,39</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr"/>
+      <c r="D9" s="5" t="n">
+        <v>1.868693341704813</v>
+      </c>
+      <c r="E9" s="5" t="inlineStr"/>
+      <c r="F9" s="5" t="n">
+        <v>2.621479929475035</v>
+      </c>
+      <c r="G9" s="6" t="inlineStr"/>
+      <c r="H9" s="6" t="inlineStr"/>
+      <c r="I9" s="6" t="inlineStr"/>
+      <c r="J9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Grupo VI</t>
+          <t>Grupo IV y V</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,299 +759,143 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>0,77</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>0,95</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
+      <c r="C10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>3.074982907251881</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="6" t="inlineStr"/>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="I10" s="6" t="inlineStr"/>
+      <c r="J10" s="6" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 3,85</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 3,74</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr"/>
+      <c r="D11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="5" t="inlineStr"/>
+      <c r="F11" s="5" t="inlineStr"/>
+      <c r="G11" s="6" t="inlineStr"/>
+      <c r="H11" s="6" t="inlineStr"/>
+      <c r="I11" s="6" t="inlineStr"/>
+      <c r="J11" s="6" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Grupo VII</t>
-        </is>
-      </c>
+      <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr"/>
+      <c r="D12" s="5" t="n">
+        <v>10.39031210644055</v>
+      </c>
+      <c r="E12" s="5" t="inlineStr"/>
+      <c r="F12" s="5" t="inlineStr"/>
+      <c r="G12" s="6" t="inlineStr"/>
+      <c r="H12" s="6" t="inlineStr"/>
+      <c r="I12" s="6" t="inlineStr"/>
+      <c r="J12" s="6" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>-0,75</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>-2,17</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>1,11</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>0,69</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-3,81; 0,0</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-7,5; 0,0</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 6,75</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 3,74</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+      <c r="C13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.7652888305071646</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>0.95495060504295</v>
+      </c>
+      <c r="G13" s="6" t="inlineStr"/>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="I13" s="6" t="inlineStr"/>
+      <c r="J13" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>No ha trabajado</t>
-        </is>
-      </c>
+      <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>-1,94</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>3,19</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>1,89</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-1,46</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr"/>
+      <c r="D14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="5" t="inlineStr"/>
+      <c r="F14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="6" t="inlineStr"/>
+      <c r="H14" s="6" t="inlineStr"/>
+      <c r="I14" s="6" t="inlineStr"/>
+      <c r="J14" s="6" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>-7,83; 0,0</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 15,54</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 9,84</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>-6,61; 0,0</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr"/>
+      <c r="D15" s="5" t="n">
+        <v>3.846866724691566</v>
+      </c>
+      <c r="E15" s="5" t="inlineStr"/>
+      <c r="F15" s="5" t="n">
+        <v>3.744642711465037</v>
+      </c>
+      <c r="G15" s="6" t="inlineStr"/>
+      <c r="H15" s="6" t="inlineStr"/>
+      <c r="I15" s="6" t="inlineStr"/>
+      <c r="J15" s="6" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Grupo VII</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1210,44 +903,32 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>-0,36</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>0,31</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>0,41</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>1,1</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>48,03%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>312,84%</t>
+      <c r="C16" s="5" t="n">
+        <v>-0.7491781207086099</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>-2.170820959218379</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>1.114984480295127</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>0.6927599319989036</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I16" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="J16" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
         </is>
       </c>
     </row>
@@ -1255,52 +936,230 @@
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>-1,27; 0,0</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>-0,72; 1,49</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 1,39</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>0,13; 2,42</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>-81,43; —</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>-40,63; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-3.808829226374589</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-7.500709188009011</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="6" t="inlineStr"/>
+      <c r="H17" s="6" t="inlineStr"/>
+      <c r="I17" s="6" t="inlineStr"/>
+      <c r="J17" s="6" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>6.751411603008599</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>3.741516935831653</v>
+      </c>
+      <c r="G18" s="6" t="inlineStr"/>
+      <c r="H18" s="6" t="inlineStr"/>
+      <c r="I18" s="6" t="inlineStr"/>
+      <c r="J18" s="6" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>-1.944570012492729</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>3.18526116169651</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>1.893080311602609</v>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>-1.464042955585052</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="I19" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="J19" s="6" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>-7.830727093170958</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="5" t="n">
+        <v>-6.61183312652218</v>
+      </c>
+      <c r="G20" s="6" t="inlineStr"/>
+      <c r="H20" s="6" t="inlineStr"/>
+      <c r="I20" s="6" t="inlineStr"/>
+      <c r="J20" s="6" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>15.54127621240022</v>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>9.839171220418386</v>
+      </c>
+      <c r="F21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="6" t="inlineStr"/>
+      <c r="H21" s="6" t="inlineStr"/>
+      <c r="I21" s="6" t="inlineStr"/>
+      <c r="J21" s="6" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>-0.3568815699905735</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>0.3113117001609779</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>0.405063067100461</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>1.102045167234383</v>
+      </c>
+      <c r="G22" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H22" s="6" t="n">
+        <v>0.4802672898022645</v>
+      </c>
+      <c r="I22" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="J22" s="6" t="n">
+        <v>3.128372848109054</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>-1.267749642151507</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>-0.7212077877835338</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>0.1273083521304812</v>
+      </c>
+      <c r="G23" s="6" t="inlineStr"/>
+      <c r="H23" s="6" t="n">
+        <v>-0.8143012206211898</v>
+      </c>
+      <c r="I23" s="6" t="inlineStr"/>
+      <c r="J23" s="6" t="n">
+        <v>-0.4062963011238719</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>1.489502473163937</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>1.385856792333274</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>2.415354506356963</v>
+      </c>
+      <c r="G24" s="6" t="inlineStr"/>
+      <c r="H24" s="6" t="inlineStr"/>
+      <c r="I24" s="6" t="inlineStr"/>
+      <c r="J24" s="6" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1308,16 +1167,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="C1:F1"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
